--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -148,6 +149,15 @@
     <t>http://terminology.hl7.org/CodeSystem/v3-RoleCode</t>
   </si>
   <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/cs/poa-privilege</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
@@ -209,6 +219,9 @@
   </si>
   <si>
     <t>power of attorney</t>
+  </si>
+  <si>
+    <t>Vendor-specific PoA privilege codes (externally governed, not enumerated)</t>
   </si>
 </sst>
 </file>
@@ -586,35 +599,75 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>43</v>
@@ -624,18 +677,18 @@
         <v>28</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>43</v>
@@ -645,18 +698,18 @@
         <v>29</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>43</v>
@@ -666,18 +719,18 @@
         <v>30</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>43</v>
@@ -687,18 +740,18 @@
         <v>31</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>43</v>
@@ -709,15 +762,15 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>43</v>
@@ -727,18 +780,18 @@
         <v>33</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>43</v>
@@ -748,18 +801,18 @@
         <v>34</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>43</v>
@@ -769,18 +822,18 @@
         <v>35</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>43</v>
@@ -790,18 +843,18 @@
         <v>36</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>43</v>
@@ -811,18 +864,18 @@
         <v>37</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>43</v>
@@ -832,18 +885,18 @@
         <v>38</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>43</v>
@@ -853,18 +906,18 @@
         <v>39</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>43</v>
@@ -874,13 +927,32 @@
         <v>40</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -9,13 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -149,6 +150,12 @@
     <t>http://terminology.hl7.org/CodeSystem/v3-RoleCode</t>
   </si>
   <si>
+    <t>PARAUTH</t>
+  </si>
+  <si>
+    <t>http://hl7.dk/fhir/core/CodeSystem/dk-relatedperson-relationshipcodes</t>
+  </si>
+  <si>
     <t>Codes</t>
   </si>
   <si>
@@ -219,6 +226,9 @@
   </si>
   <si>
     <t>power of attorney</t>
+  </si>
+  <si>
+    <t>parental authority</t>
   </si>
   <si>
     <t>Vendor-specific PoA privilege codes (externally governed, not enumerated)</t>
@@ -608,13 +618,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>45</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -629,7 +643,7 @@
         <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -639,35 +653,75 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>43</v>
@@ -677,18 +731,18 @@
         <v>28</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>43</v>
@@ -698,18 +752,18 @@
         <v>29</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>43</v>
@@ -719,18 +773,18 @@
         <v>30</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>43</v>
@@ -740,18 +794,18 @@
         <v>31</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>43</v>
@@ -762,15 +816,15 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>43</v>
@@ -780,18 +834,18 @@
         <v>33</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>43</v>
@@ -801,18 +855,18 @@
         <v>34</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>43</v>
@@ -822,18 +876,18 @@
         <v>35</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>43</v>
@@ -843,18 +897,18 @@
         <v>36</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>43</v>
@@ -864,18 +918,18 @@
         <v>37</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>43</v>
@@ -885,18 +939,18 @@
         <v>38</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>43</v>
@@ -906,18 +960,18 @@
         <v>39</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>43</v>
@@ -927,32 +981,53 @@
         <v>40</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>44</v>
+      </c>
       <c r="E15" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>56</v>
+      <c r="G16" t="s" s="2">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-relatedperson-relationshiptype.xlsx
+++ b/fhir/ValueSet-relatedperson-relationshiptype.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
